--- a/Config/Datas/ReputationDatas/ReputationDatas.xlsx
+++ b/Config/Datas/ReputationDatas/ReputationDatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\ReputationDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B35BF47-DE83-41B7-9746-ED6B1B9B6F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531218EE-0693-46AF-8081-9A162C86F494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,10 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无人问津</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>默默无闻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,6 +124,43 @@
   </si>
   <si>
     <t>物品刷新率：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查无此人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_修改稀有度概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.65|0.35|0|0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得收入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.55|0.35|0.1|0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4|0.4|0.15|0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品刷新率：
+&lt;color=green&gt;65%&lt;/color&gt; &lt;color=blue&gt;35%&lt;/color&gt; &lt;color=purple&gt;0%&lt;/color&gt; &lt;color=yellow&gt;0%&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -187,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -200,6 +233,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,14 +517,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
+    <col min="4" max="4" width="7.08203125" customWidth="1"/>
     <col min="7" max="7" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,19 +546,19 @@
       <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -556,19 +592,19 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
       <c r="M3" s="4" t="s">
         <v>12</v>
       </c>
@@ -576,19 +612,19 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
       <c r="M4" s="4" t="s">
         <v>14</v>
       </c>
@@ -596,91 +632,152 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="70" x14ac:dyDescent="0.3">
+      <c r="G6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B7">
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
       </c>
-      <c r="D7">
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H12">
         <v>2</v>
       </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B9">
+      <c r="D14">
         <v>4</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B10">
+      <c r="D15">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
         <v>20</v>
       </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13">
+      <c r="D18">
         <v>7</v>
       </c>
     </row>

--- a/Config/Datas/ReputationDatas/ReputationDatas.xlsx
+++ b/Config/Datas/ReputationDatas/ReputationDatas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\ReputationDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531218EE-0693-46AF-8081-9A162C86F494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D9E685-6040-4CF8-A142-0117D8A5A55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>广受好评</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>串界权威</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,14 +116,6 @@
   </si>
   <si>
     <t>收入+3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品刷新率：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查无此人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -161,6 +149,20 @@
   <si>
     <t>物品刷新率：
 &lt;color=green&gt;65%&lt;/color&gt; &lt;color=blue&gt;35%&lt;/color&gt; &lt;color=purple&gt;0%&lt;/color&gt; &lt;color=yellow&gt;0%&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品刷新率：
+&lt;color=green&gt;55%&lt;/color&gt; &lt;color=blue&gt;35%&lt;/color&gt; &lt;color=purple&gt;10%&lt;/color&gt; &lt;color=yellow&gt;0%&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品刷新率：
+&lt;color=green&gt;40%&lt;/color&gt; &lt;color=blue&gt;40%&lt;/color&gt; &lt;color=purple&gt;15%&lt;/color&gt; &lt;color=yellow&gt;5%&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -517,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="7.08203125" customWidth="1"/>
@@ -637,36 +639,39 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="70" x14ac:dyDescent="0.3">
       <c r="G6" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -674,36 +679,39 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G9" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="70" x14ac:dyDescent="0.3">
+      <c r="G9" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="M9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" t="s">
         <v>26</v>
-      </c>
-      <c r="N9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -711,30 +719,39 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
+      <c r="F11">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="70" x14ac:dyDescent="0.3">
+      <c r="G12" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H12">
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -742,42 +759,54 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B15">
+      <c r="F14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B18">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D15">
+      <c r="D18">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16">
+      <c r="F18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16">
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21">
         <v>7</v>
       </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18">
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
         <v>7</v>
       </c>
     </row>

--- a/Config/Datas/ReputationDatas/ReputationDatas.xlsx
+++ b/Config/Datas/ReputationDatas/ReputationDatas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\ReputationDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D9E685-6040-4CF8-A142-0117D8A5A55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0060449B-006B-4698-AC92-CA5BA7A4D06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +163,14 @@
   </si>
   <si>
     <t>##</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择一张卡牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_随机选卡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -674,6 +682,20 @@
         <v>24</v>
       </c>
     </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2</v>
@@ -712,6 +734,20 @@
       </c>
       <c r="N9" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
